--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2021_o higgins.xlsx
@@ -123,18 +123,18 @@
     <t xml:space="preserve">Pichilemu</t>
   </si>
   <si>
+    <t xml:space="preserve">Machalí</t>
+  </si>
+  <si>
     <t xml:space="preserve">Marchigüe</t>
   </si>
   <si>
+    <t xml:space="preserve">Palmilla</t>
+  </si>
+  <si>
     <t xml:space="preserve">Codegua</t>
   </si>
   <si>
-    <t xml:space="preserve">Palmilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Machalí</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:15</t>
+    <t xml:space="preserve">2026-09-10 00:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1067,7 +1067,7 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>6204</v>
+        <v>6108</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
@@ -1080,7 +1080,7 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>6102</v>
+        <v>6204</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
@@ -1106,7 +1106,7 @@
         <v>38</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>6108</v>
+        <v>6102</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>

--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2021_o higgins.xlsx
@@ -45,6 +45,9 @@
     <t xml:space="preserve">Chépica</t>
   </si>
   <si>
+    <t xml:space="preserve">Marchigüe</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Fernando</t>
   </si>
   <si>
@@ -126,9 +129,6 @@
     <t xml:space="preserve">Machalí</t>
   </si>
   <si>
-    <t xml:space="preserve">Marchigüe</t>
-  </si>
-  <si>
     <t xml:space="preserve">Palmilla</t>
   </si>
   <si>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:19</t>
+    <t xml:space="preserve">2026-09-18 10:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -625,13 +625,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>6301</v>
+        <v>6204</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>59.71</v>
+        <v>61.81</v>
       </c>
     </row>
     <row r="6">
@@ -642,13 +642,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>6105</v>
+        <v>6301</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>59.6</v>
+        <v>59.71</v>
       </c>
     </row>
     <row r="7">
@@ -659,13 +659,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>6305</v>
+        <v>6105</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>58.94</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="8">
@@ -676,13 +676,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>6310</v>
+        <v>6305</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>58.51</v>
+        <v>58.94</v>
       </c>
     </row>
     <row r="9">
@@ -693,13 +693,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>6114</v>
+        <v>6310</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>58.44</v>
+        <v>58.51</v>
       </c>
     </row>
     <row r="10">
@@ -710,13 +710,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>6115</v>
+        <v>6114</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>57.9</v>
+        <v>58.44</v>
       </c>
     </row>
     <row r="11">
@@ -727,13 +727,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>6116</v>
+        <v>6115</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>57.76</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="12">
@@ -744,13 +744,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>6112</v>
+        <v>6116</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>57.51</v>
+        <v>57.76</v>
       </c>
     </row>
     <row r="13">
@@ -761,13 +761,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>6308</v>
+        <v>6112</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>57.06</v>
+        <v>57.51</v>
       </c>
     </row>
     <row r="14">
@@ -778,13 +778,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>6103</v>
+        <v>6308</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>57.05</v>
+        <v>57.06</v>
       </c>
     </row>
     <row r="15">
@@ -795,13 +795,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>6303</v>
+        <v>6103</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>56.66</v>
+        <v>57.05</v>
       </c>
     </row>
     <row r="16">
@@ -812,13 +812,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>6117</v>
+        <v>6303</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>56.14</v>
+        <v>56.66</v>
       </c>
     </row>
     <row r="17">
@@ -829,13 +829,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>6203</v>
+        <v>6117</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>55.53</v>
+        <v>56.14</v>
       </c>
     </row>
     <row r="18">
@@ -846,13 +846,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>6113</v>
+        <v>6203</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>55.13</v>
+        <v>55.53</v>
       </c>
     </row>
     <row r="19">
@@ -863,13 +863,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>6106</v>
+        <v>6113</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>54.84</v>
+        <v>55.13</v>
       </c>
     </row>
     <row r="20">
@@ -880,7 +880,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>6304</v>
+        <v>6106</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2021</v>
@@ -897,13 +897,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>6111</v>
+        <v>6304</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>54.2</v>
+        <v>54.84</v>
       </c>
     </row>
     <row r="22">
@@ -914,13 +914,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>6104</v>
+        <v>6111</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>53.98</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="23">
@@ -931,13 +931,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>6109</v>
+        <v>6104</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>53.96</v>
+        <v>53.98</v>
       </c>
     </row>
     <row r="24">
@@ -948,13 +948,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>6110</v>
+        <v>6109</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>53.55</v>
+        <v>53.96</v>
       </c>
     </row>
     <row r="25">
@@ -965,13 +965,13 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>6101</v>
+        <v>6110</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>52.29</v>
+        <v>53.55</v>
       </c>
     </row>
     <row r="26">
@@ -982,13 +982,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>6107</v>
+        <v>6101</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>50.12</v>
+        <v>52.29</v>
       </c>
     </row>
     <row r="27">
@@ -999,13 +999,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>6205</v>
+        <v>6107</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>49.53</v>
+        <v>50.12</v>
       </c>
     </row>
     <row r="28">
@@ -1016,13 +1016,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>6309</v>
+        <v>6205</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>48.57</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="29">
@@ -1033,13 +1033,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>6206</v>
+        <v>6309</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>47.37</v>
+        <v>48.57</v>
       </c>
     </row>
     <row r="30">
@@ -1050,13 +1050,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>6201</v>
+        <v>6206</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>46.86</v>
+        <v>47.37</v>
       </c>
     </row>
     <row r="31">
@@ -1067,10 +1067,14 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>6108</v>
-      </c>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
+        <v>6201</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>46.86</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
@@ -1080,7 +1084,7 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>6204</v>
+        <v>6108</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
